--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784689</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784689</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784689</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784689</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784683</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784682</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784686</v>
       </c>
       <c r="B6" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784684</v>
       </c>
       <c r="B7" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135784688</v>
       </c>
       <c r="B8" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784689</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135784687</v>
       </c>
       <c r="B10" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12736-2026 artfynd.xlsx
+++ b/artfynd/A 12736-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135784685</v>
       </c>
       <c r="B3" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784681</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
